--- a/seikyu/tests/fixtures/seikyu-customer-template.xlsx
+++ b/seikyu/tests/fixtures/seikyu-customer-template.xlsx
@@ -51,7 +51,7 @@
     <t>A-0001</t>
   </si>
   <si>
-    <t>藤原建設株式会社 御中</t>
+    <t>標様建設株式会社 御中</t>
   </si>
   <si>
     <t>登録番号</t>
